--- a/forms/trg/Formulir_TRG_iorg.xlsx
+++ b/forms/trg/Formulir_TRG_iorg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. dr. Upik A. Miskad, PhD, SpPA (K)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Department of Anatomical Pathology, Faculty of Medicine Hasanuddin University, Makassar Indonesia</t>
@@ -959,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1004,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1041,7 +1045,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1082,7 +1086,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1123,7 +1127,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1271,7 +1275,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1304,7 +1308,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1341,7 +1345,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1378,7 +1382,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
